--- a/pay-template.xlsx
+++ b/pay-template.xlsx
@@ -2295,7 +2295,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="239">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -2905,6 +2905,9 @@
     <xf numFmtId="14" fontId="32" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="2" fillId="3" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3105,7 +3108,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:srcRect r="50872" b="-6110"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3113,7 +3115,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="2956560" cy="800100"/>
+          <a:ext cx="2679600" cy="800100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3785,14 +3787,18 @@
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:8" s="11" customFormat="1" ht="14">
-      <c r="A28" s="134" t="s">
+      <c r="A28" s="239" t="s">
         <v>143</v>
       </c>
-      <c r="B28" s="126" t="s">
+      <c r="B28" s="239" t="s">
         <v>138</v>
       </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="168" t="s">
+      <c r="C28" s="239" t="inlineStr">
+        <is>
+          <t>HỒ THANH TÂM</t>
+        </is>
+      </c>
+      <c r="D28" s="239" t="s">
         <v>142</v>
       </c>
       <c r="E28" s="168"/>

--- a/pay-template.xlsx
+++ b/pay-template.xlsx
@@ -1626,16 +1626,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1665,7 +1663,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Times New Roman"/>
       <family val="2"/>
     </font>
     <font>
@@ -1857,9 +1855,8 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1870,7 +1867,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="TimesNewRomanRegular"/>
+      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="8">
@@ -2906,7 +2903,7 @@
     <xf numFmtId="166" fontId="2" fillId="3" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
